--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.12" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.13" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.14" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.15" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="40">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -280,6 +281,16 @@
       <name val="Microsoft YaHei"/>
       <color rgb="00A8A29E"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -786,7 +797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -845,6 +856,9 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2130,6 +2144,1150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>7.15 训练强度报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>25人  训练  RPE≈5.8(3-8)  sRPE≈8780  睡2.5  疲2.2  酸2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>今天怎么了</t>
+        </is>
+      </c>
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t>明天怎么调</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H5" t="n">
+        <v>360</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>酸痛偏高</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>关注恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H6" t="n">
+        <v>360</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>疲劳酸痛偏高</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>减量10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>疲劳酸痛偏高</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>减量10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>480</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>高负荷+脚踝不适 ⚠️</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>减量20%，冰敷脚踝</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>360</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>360</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>停赛中</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>维持训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>360</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>睡眠略差</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>多睡30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="n">
+        <v>300</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>酸痛未填</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>追问酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>360</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>左膝持续疼痛 ⚠️</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>离心训练+冰敷</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>360</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>睡眠略差</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>多睡30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>300</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>停赛中</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>维持训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>360</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>360</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>疲劳偏高</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>减量10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>继续康复</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>360</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>睡眠差+脚掌骨疼 ⚠️</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>减量+检查脚掌</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="n">
+        <v>360</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" t="n">
+        <v>360</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>睡眠略差</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>多睡30min</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="n">
+        <v>360</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>睡眠差</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>多睡1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="n">
+        <v>420</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>睡眠差+负荷偏高</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>减量15%+多睡</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" t="n">
+        <v>125</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>部分参与·疲劳偏高</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>正常恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>45</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>发烧 🔴</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>休息+就医</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" t="n">
+        <v>360</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>状态满分</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>保持</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="n">
+        <v>420</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>负荷偏高</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>减量10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" t="n">
+        <v>360</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="n">
+        <v>480</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>高负荷+睡眠略差</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>减量20%+早睡</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H30" t="n">
+        <v>75</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>部分参与</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>刘子结</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>25</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>试训·部分参与</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>试训·部分参与</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>🔴 红旗: 朱云天(发烧) 巫林峰(脚掌骨+睡眠4) 张俊哲(脚踝+RPE8) 王捷(左膝持续) 阿西江(RPE8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>⚠️ 关注: 杨翼璇(睡4+RPE7) 栾昊(睡4) 杨卓燠/王款(疲劳3+酸痛3)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26人晨间: 睡2.6 疲2.2 酸2.0</t>
+          <t>28人晨间: 睡2.7 疲2.2 酸2.0</t>
         </is>
       </c>
     </row>
@@ -4675,9 +4675,18 @@
           <t>后卫</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -4858,17 +4867,16 @@
           <t>中场</t>
         </is>
       </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>睡眠未填</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4902,9 +4910,18 @@
           <t>中场</t>
         </is>
       </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -5076,6 +5093,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.15" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.16" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.17" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.18" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -339,6 +340,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -831,7 +835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -899,6 +903,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4876,7 +4881,6 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5093,7 +5097,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -5112,6 +5115,1027 @@
       <c r="A37" t="inlineStr">
         <is>
           <t>💡明日MD-1: 轻量激活+定位球演练；6名标记球员单独评估后决定出战名单</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>7月18日 每日强度监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MD-1 · 客场备战大连英博B · 55min · 22人参训 · 均RPE 3.6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26人晨间: 睡2.7 疲2.2 酸1.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
+        <is>
+          <t>问题/风险</t>
+        </is>
+      </c>
+      <c r="J4" s="29" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H5" t="n">
+        <v>110</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>脚踝痛·第4天(门将出战风险)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>赛前三步测试(提踵→跳→侧蹬)再定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55</v>
+      </c>
+      <c r="H6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>110</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>330</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>220</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>220</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>275</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>220</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>左膝持续</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>赛前等长止痛；离心留到赛后</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>55</v>
+      </c>
+      <c r="H14" t="n">
+        <v>275</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
+        <v>330</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>太原基地·未随队</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>220</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H19" t="n">
+        <v>220</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>脚掌骨疼·第4天</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>赛中锐痛→换人；赛后加重建议影像</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>55</v>
+      </c>
+      <c r="H20" t="n">
+        <v>220</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>220</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>内踝还有点疼(7月第2次)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>赛前弹力带内翻+平衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>55</v>
+      </c>
+      <c r="H22" t="n">
+        <v>165</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>55</v>
+      </c>
+      <c r="H23" t="n">
+        <v>220</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>55</v>
+      </c>
+      <c r="H24" t="n">
+        <v>165</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>太原基地·未随队</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>太原基地·未随队</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>55</v>
+      </c>
+      <c r="H28" t="n">
+        <v>165</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>55</v>
+      </c>
+      <c r="H29" t="n">
+        <v>165</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>左后群轻微紧点</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>赛前冲刺三段自测；发紧降速</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" t="n">
+        <v>165</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>55</v>
+      </c>
+      <c r="H31" t="n">
+        <v>165</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>太原基地·未随队</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>55</v>
+      </c>
+      <c r="H33" t="n">
+        <v>110</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>🟢 MD-1轻量激活 | 均RPE 3.6 总sRPE 4400 | 🟢低强度(全队sRPE&lt;300)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>赛前风险(5人): 张海轩脚踝D4(门将) 王捷左膝 巫林峰脚掌 谢锦政内踝 艾沙江左后群 | 何麟立腘绳肌已恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>明日比赛日: 张海轩赛前三步测试；巫林峰脚掌锐痛→立即换人；腘绳肌组冲刺前自测</t>
         </is>
       </c>
     </row>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10260" tabRatio="600" firstSheet="2" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10260" tabRatio="600" firstSheet="2" activeTab="16" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.18" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.19" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.20" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.22" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.23" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="44">
+  <fonts count="48">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -332,8 +334,28 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -538,8 +560,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00992828"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -674,6 +701,20 @@
         <color theme="4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -823,7 +864,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -896,6 +937,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="35" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7054,7 +7106,6 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -7666,6 +7717,2635 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>7月22日 每日强度监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>上午力量房60min·12站U-L交替·31人·均RPE≈4.5 | 下午场地70min·动态拉伸→抢圈→传接球→射门专项(2线路)→13v13+4GK·均RPE≈4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="inlineStr">
+        <is>
+          <t>问题/风险</t>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>360</v>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>脚踝痛D9</t>
+        </is>
+      </c>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>维持康复方案·冰敷·下午场地评估 | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" s="33" t="inlineStr"/>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="33" t="inlineStr"/>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>新人适应</t>
+        </is>
+      </c>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>轻量·重技术学习 | 场地RPE=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>360</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>RPE=10→6 恢复中</t>
+        </is>
+      </c>
+      <c r="J9" s="33" t="inlineStr">
+        <is>
+          <t>继续降量·关注疲劳 | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr"/>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>停赛休足·状态极佳</t>
+        </is>
+      </c>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>正常训练 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr"/>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>睡4→3 改善中</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>继续降量 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>左膝髌腱</t>
+        </is>
+      </c>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>康复方案·冰敷 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>疲4→3 恢复中</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>继续降量 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>睡4</t>
+        </is>
+      </c>
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>关注睡眠 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I17" s="33" t="inlineStr"/>
+      <c r="J17" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I18" s="33" t="inlineStr"/>
+      <c r="J18" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>⚠️睡5 睡眠严重不足</t>
+        </is>
+      </c>
+      <c r="J19" s="33" t="inlineStr">
+        <is>
+          <t>调查原因·降量·下午观察 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>布格拉汗</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>MCL归队D2·力量房OK</t>
+        </is>
+      </c>
+      <c r="J20" s="33" t="inlineStr">
+        <is>
+          <t>维持康复方案·冰敷·下午场地单独</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>脚掌史</t>
+        </is>
+      </c>
+      <c r="J21" s="33" t="inlineStr">
+        <is>
+          <t>康复方案·坐姿优先·冰敷 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>🆕脚腕疼·新信号</t>
+        </is>
+      </c>
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>关注·如持续建议评估 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I23" s="33" t="inlineStr">
+        <is>
+          <t>内踝已恢复</t>
+        </is>
+      </c>
+      <c r="J23" s="33" t="inlineStr">
+        <is>
+          <t>正常训练 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I24" s="33" t="inlineStr"/>
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I25" s="33" t="inlineStr"/>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I26" s="33" t="inlineStr"/>
+      <c r="J26" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I27" s="33" t="inlineStr"/>
+      <c r="J27" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>360</v>
+      </c>
+      <c r="I28" s="33" t="inlineStr">
+        <is>
+          <t>新人·训练投入高</t>
+        </is>
+      </c>
+      <c r="J28" s="33" t="inlineStr">
+        <is>
+          <t>控制强度·避免过度 | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>新人·轻量</t>
+        </is>
+      </c>
+      <c r="J29" s="33" t="inlineStr">
+        <is>
+          <t>正常适应 | 场地RPE=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>新人·RPE待补</t>
+        </is>
+      </c>
+      <c r="J30" s="33" t="inlineStr">
+        <is>
+          <t>补填RPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I31" s="33" t="inlineStr"/>
+      <c r="J31" s="33" t="inlineStr">
+        <is>
+          <t>降量50% | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>艾沙江</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H32" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>后群紧·观察中</t>
+        </is>
+      </c>
+      <c r="J32" s="33" t="inlineStr">
+        <is>
+          <t>臀桥代深蹲·不硬拉·下午观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H33" s="34" t="n">
+        <v>360</v>
+      </c>
+      <c r="I33" s="33" t="inlineStr">
+        <is>
+          <t>三高→改善(疲4→3)</t>
+        </is>
+      </c>
+      <c r="J33" s="33" t="inlineStr">
+        <is>
+          <t>继续降量·睡4仍需关注</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I34" s="33" t="inlineStr"/>
+      <c r="J34" s="33" t="inlineStr">
+        <is>
+          <t>降量50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>努尔扎提</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I35" s="33" t="inlineStr"/>
+      <c r="J35" s="33" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>AM力量房(均RPE≈4.5)+PM场地70min(均RPE≈4.5) | 一日双训·MD-4维持 | 🆕张辉脚腕疼 | ⚠️何麟立睡5 | 布格拉汗归队D2全天✅ | 场地:13v13+4GK·射门2线路</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>7月23日 每日强度监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>MD-3 · 场地50min · 头球游戏9min+11v11自由人×2(6min×2)+11v11三球门20min · 同步4v4 · 备战7/26主场vs南通海门</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>全队均RPE≈5.7 · 均sRPE≈290 · ⚠️张俊哲RPE=8 · 张辉/王皓文/李金羽/王捷/凌中阳/丁云峰RPE=7 · 7/22力量房过量的叠加效应显现</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="32" t="n">
+        <v>350</v>
+      </c>
+      <c r="I4" s="32" t="inlineStr">
+        <is>
+          <t>脚踝痛D10·RPE=7偏高</t>
+        </is>
+      </c>
+      <c r="J4" s="32" t="inlineStr">
+        <is>
+          <t>继续踝泵·冰敷·明天降量</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>肩膀疼</t>
+        </is>
+      </c>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>观察·正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I6" s="33" t="inlineStr"/>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>新人·睡眠缺填</t>
+        </is>
+      </c>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t>补填晨间问卷</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>400</v>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>⚠️⚠️⚠️ RPE=8全队最高·7/19跑10km⚡+7/22全量力量→累积疲劳</t>
+        </is>
+      </c>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>D-3/D-2必须降量·软组织放松·明天单独评估·如RPE仍≥7建议7/26替补</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I9" s="33" t="inlineStr"/>
+      <c r="J9" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>停赛休足·三球门覆盖面积大</t>
+        </is>
+      </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>正常训练反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I11" s="33" t="inlineStr"/>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 连续两天RPE偏高(5→7)·睡3疲3</t>
+        </is>
+      </c>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>关注恢复·明天评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 左膝酸痛=4(昨1→今4)·RPE=7</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>髌腱负荷可能过大·明天评估离心训练量·如持续加重建议减量</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>正常酸痛·RPE偏高</t>
+        </is>
+      </c>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>正常训练反应·明天观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>正常酸痛·RPE偏高</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>正常训练反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>4v4(前10min)→主组</t>
+        </is>
+      </c>
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>4v4组</t>
+        </is>
+      </c>
+      <c r="J17" s="33" t="inlineStr">
+        <is>
+          <t>投入正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>睡眠5→2·大幅改善✅</t>
+        </is>
+      </c>
+      <c r="J18" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>MCL D+2·4v4参与</t>
+        </is>
+      </c>
+      <c r="J19" s="33" t="inlineStr">
+        <is>
+          <t>变向可控✅·继续康复方案·冰敷</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>脚掌史·正常训练</t>
+        </is>
+      </c>
+      <c r="J20" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 肌肉酸·7/19跑10km⚡+脚腕疼史</t>
+        </is>
+      </c>
+      <c r="J21" s="33" t="inlineStr">
+        <is>
+          <t>监控·明天评估·如持续建议影像</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>疲劳缺填·内踝已恢复</t>
+        </is>
+      </c>
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>补填·正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I23" s="33" t="inlineStr"/>
+      <c r="J23" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" s="33" t="inlineStr"/>
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>4v4组·酸痛=4</t>
+        </is>
+      </c>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t>正常训练反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>200</v>
+      </c>
+      <c r="I26" s="33" t="inlineStr">
+        <is>
+          <t>4v4组</t>
+        </is>
+      </c>
+      <c r="J26" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 睡4+RPE=2·投入度待观察</t>
+        </is>
+      </c>
+      <c r="J27" s="33" t="inlineStr">
+        <is>
+          <t>关注睡眠恶化和低投入度·明天沟通</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" s="33" t="inlineStr">
+        <is>
+          <t>4v4组·10min替换</t>
+        </is>
+      </c>
+      <c r="J28" s="33" t="inlineStr">
+        <is>
+          <t>新人适应·正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>180</v>
+      </c>
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>新人·全部缺填</t>
+        </is>
+      </c>
+      <c r="J29" s="33" t="inlineStr">
+        <is>
+          <t>提醒补填</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>恢复良好✅</t>
+        </is>
+      </c>
+      <c r="J30" s="33" t="inlineStr">
+        <is>
+          <t>正常·RPE回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I31" s="33" t="inlineStr">
+        <is>
+          <t>后群观察中</t>
+        </is>
+      </c>
+      <c r="J31" s="33" t="inlineStr">
+        <is>
+          <t>正常训练·持续监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>睡眠4→3改善·RPE稳定</t>
+        </is>
+      </c>
+      <c r="J32" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I33" s="33" t="inlineStr"/>
+      <c r="J33" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="34" t="n">
+        <v>240</v>
+      </c>
+      <c r="I34" s="33" t="inlineStr">
+        <is>
+          <t>未填数据·待补</t>
+        </is>
+      </c>
+      <c r="J34" s="33" t="inlineStr">
+        <is>
+          <t>提醒补填</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>300</v>
+      </c>
+      <c r="I35" s="33" t="inlineStr"/>
+      <c r="J35" s="33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>7/23 MD-3 · 头球+三球门11v11+4v4 · 均RPE≈5.7 · ⚠️张俊哲RPE=8(累积疲劳)·王捷膝酸痛突增(1→4)·张辉肌肉酸·7/22力量房过量叠加效应 · 7/26主场vs海门</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="20" activeTab="22" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="20" activeTab="32" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.6" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.7" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -4451,7 +4452,6 @@
       </c>
       <c r="H32" s="20" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -4514,7 +4514,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -5267,7 +5266,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -5330,7 +5328,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -6295,7 +6292,6 @@
       <c r="I33" s="19" t="inlineStr"/>
       <c r="J33" s="19" t="inlineStr"/>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -6353,7 +6349,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -7232,7 +7227,6 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -7283,7 +7277,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -7829,7 +7822,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -7873,7 +7865,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -9132,7 +9123,6 @@
       <c r="I35" s="15" t="inlineStr"/>
       <c r="J35" s="15" t="inlineStr"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
@@ -12699,7 +12689,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -16315,7 +16304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17280,7 +17269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -23746,7 +23735,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -27493,6 +27481,930 @@
       </c>
       <c r="I31" s="19" t="inlineStr"/>
       <c r="J31" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>今天问题</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>明天建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H2" t="n">
+        <v>760</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H3" t="n">
+        <v>760</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>84</v>
+      </c>
+      <c r="H4" t="n">
+        <v>672</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>95</v>
+      </c>
+      <c r="H5" t="n">
+        <v>950</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RPE=10·全倾</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>D+1泳池恢复优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>760</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>95</v>
+      </c>
+      <c r="H7" t="n">
+        <v>760</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>440</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>950</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RPE=10·全倾</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>D+1泳池恢复优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>855</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>95</v>
+      </c>
+      <c r="H11" t="n">
+        <v>855</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>首发高强度</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>855</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>进球·RPE=9</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>充分恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="n">
+        <v>320</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>66</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>60</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>45</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>45</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>60</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>45</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>45</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>60</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29440,7 +30352,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -30611,7 +31522,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="17.6" customHeight="1">
       <c r="A30" s="36" t="inlineStr">
         <is>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -27562,9 +27562,15 @@
       <c r="C2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
       <c r="G2" t="n">
         <v>95</v>
       </c>
@@ -27596,9 +27602,15 @@
       <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" t="n">
         <v>95</v>
       </c>
@@ -27630,9 +27642,15 @@
       <c r="C4" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" t="n">
         <v>84</v>
       </c>
@@ -27664,9 +27682,15 @@
       <c r="C5" t="n">
         <v>10</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" t="n">
         <v>95</v>
       </c>
@@ -27698,9 +27722,15 @@
       <c r="C6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" t="n">
         <v>95</v>
       </c>
@@ -27732,9 +27762,15 @@
       <c r="C7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
       <c r="G7" t="n">
         <v>95</v>
       </c>
@@ -27766,9 +27802,15 @@
       <c r="C8" t="n">
         <v>8</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" t="n">
         <v>55</v>
       </c>
@@ -27800,9 +27842,15 @@
       <c r="C9" t="n">
         <v>10</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
       <c r="G9" t="n">
         <v>95</v>
       </c>
@@ -27834,9 +27882,15 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" t="n">
         <v>95</v>
       </c>
@@ -27868,9 +27922,15 @@
       <c r="C11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
       <c r="G11" t="n">
         <v>95</v>
       </c>
@@ -27902,9 +27962,15 @@
       <c r="C12" t="n">
         <v>9</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
       <c r="G12" t="n">
         <v>95</v>
       </c>
@@ -27936,17 +28002,21 @@
       <c r="C13" t="n">
         <v>8</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
       <c r="G13" t="n">
         <v>40</v>
       </c>
       <c r="H13" t="n">
         <v>320</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27962,17 +28032,21 @@
       <c r="C14" t="n">
         <v>6</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
       <c r="G14" t="n">
         <v>11</v>
       </c>
       <c r="H14" t="n">
         <v>66</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27988,17 +28062,21 @@
       <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
       <c r="G15" t="n">
         <v>15</v>
       </c>
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -28014,17 +28092,21 @@
       <c r="C16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -28040,17 +28122,21 @@
       <c r="C17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" t="n">
         <v>15</v>
       </c>
       <c r="H17" t="n">
         <v>45</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28066,17 +28152,21 @@
       <c r="C18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
       <c r="G18" t="n">
         <v>15</v>
       </c>
       <c r="H18" t="n">
         <v>45</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -28092,17 +28182,21 @@
       <c r="C19" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" t="n">
         <v>15</v>
       </c>
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -28118,17 +28212,21 @@
       <c r="C20" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
       <c r="G20" t="n">
         <v>15</v>
       </c>
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -28144,17 +28242,21 @@
       <c r="C21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" t="n">
         <v>15</v>
       </c>
       <c r="H21" t="n">
         <v>45</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -28170,17 +28272,21 @@
       <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
       <c r="G22" t="n">
         <v>15</v>
       </c>
       <c r="H22" t="n">
         <v>45</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -28196,17 +28302,21 @@
       <c r="C23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
       <c r="G23" t="n">
         <v>15</v>
       </c>
       <c r="H23" t="n">
         <v>45</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -28222,17 +28332,21 @@
       <c r="C24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" t="n">
         <v>15</v>
       </c>
       <c r="H24" t="n">
         <v>60</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -28248,17 +28362,21 @@
       <c r="C25" t="n">
         <v>3</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -28274,17 +28392,18 @@
       <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -28297,18 +28416,11 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -28321,18 +28433,11 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -28345,18 +28450,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -28369,18 +28467,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -28393,18 +28484,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="33" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="34" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -28666,8 +28667,6 @@
       <c r="H4" t="n">
         <v>120</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28698,25 +28697,966 @@
       <c r="H5" t="n">
         <v>180</v>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
+      </c>
+      <c r="H11" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="n">
+        <v>180</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>脚踝痛D6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>继续冰敷+踝泵</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="n">
+        <v>120</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>脚腕微痛🆕</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="n">
+        <v>300</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RPE=5·赛前MCL疼</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>D+3降负荷·避免冲刺</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MD-3</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>训练50min</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>脚踝疼持续5天</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>持续观察，赛前评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>150</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>努尔扎提-努尔兰</t>
+          <t>王款(U21)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>门将</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -28725,10 +29665,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -28736,12 +29676,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>吕佳骏</t>
+          <t>王熙博</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>门将</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -28757,10 +29697,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -28768,31 +29708,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>巫林峰</t>
+          <t>张俊哲</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -28800,16 +29740,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>布格拉汗-斯坎旦尔</t>
+          <t>张天龙</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -28821,10 +29761,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -28832,31 +29772,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>帕尔曼江-克尤木</t>
+          <t>凌中阳</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -28864,12 +29804,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>张俊哲</t>
+          <t>陈少豪</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -28879,16 +29819,16 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H11" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -28896,16 +29836,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>张天龙</t>
+          <t>李金羽</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -28917,10 +29857,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -28928,12 +29868,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>张海轩</t>
+          <t>王捷(U21)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -28943,128 +29883,136 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>脚踝痛D6</t>
+          <t>左膝髌腱炎持续</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>继续冰敷+踝泵</t>
+          <t>控制跳跃急停负荷</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>张辉</t>
+          <t>王皓文(U21)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>脚腕微痛🆕</t>
+          <t>RPE偏高</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>MD-3窗口内可接受</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>朱云天(U21)</t>
+          <t>丁云峰</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H15" t="n">
-        <v>180</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>睡眠4偏高</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>关注恢复</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>杨卓燠</t>
+          <t>杨文杰</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>后卫</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -29072,51 +30020,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>杨文杰</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
-      </c>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>60</v>
-      </c>
-      <c r="H17" t="n">
-        <v>180</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>未参训</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>杨翼璇</t>
+          <t>何麟立</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -29125,30 +30067,38 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H18" t="n">
-        <v>120</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>内收肌还是有点紧</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>持续关注，MD-2减量</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>林楷轩(U21)</t>
+          <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -29157,10 +30107,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -29168,19 +30118,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>栾昊(U21)</t>
+          <t>巫林峰</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -29189,10 +30139,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -29200,49 +30150,55 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>王捷(U21)</t>
+          <t>张辉</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H21" t="n">
-        <v>180</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>本周最高RPE</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MD-3峰值可接受</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>王款(U21)</t>
+          <t>谢锦政</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GK</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>2</v>
       </c>
@@ -29252,31 +30208,35 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="n">
-        <v>60</v>
-      </c>
-      <c r="H22" t="n">
-        <v>120</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>脚趾恢复中，未参训</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>继续观察</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>王熙博</t>
+          <t>栾昊(U21)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -29285,10 +30245,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H23" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -29296,31 +30256,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>王皓文(U21)</t>
+          <t>杨翼璇</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H24" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -29328,116 +30288,108 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>艾沙江-库尔班</t>
+          <t>林楷轩(U21)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H25" t="n">
-        <v>300</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>RPE=5·赛前MCL疼</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>D+3降负荷·避免冲刺</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>阿西江-白山</t>
+          <t>朱云天(U21)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
-        <v>180</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>本周最高RPE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MD-3峰值可接受</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>陈少豪</t>
+          <t>董德</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>60</v>
-      </c>
-      <c r="H27" t="n">
-        <v>120</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未参训</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>陈祥煜</t>
+          <t>吕佳骏</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>中场</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -29453,10 +30405,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -29464,15 +30416,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>谢锦政</t>
+          <t>陈祥煜</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
@@ -29480,64 +30434,152 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="n">
+        <v>150</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>李金羽</t>
+          <t>艾沙江-库尔班</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" t="n">
+        <v>250</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>疲劳酸痛偏高</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MCL史，关注</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>董德</t>
+          <t>帕尔曼江-克尤木</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" t="n">
+        <v>200</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" t="n">
+        <v>200</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" t="n">
+        <v>200</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -29638,8 +29638,6 @@
       <c r="H5" t="n">
         <v>150</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29670,8 +29668,6 @@
       <c r="H6" t="n">
         <v>150</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29702,8 +29698,6 @@
       <c r="H7" t="n">
         <v>100</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29734,8 +29728,6 @@
       <c r="H8" t="n">
         <v>150</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29766,8 +29758,6 @@
       <c r="H9" t="n">
         <v>200</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29798,8 +29788,6 @@
       <c r="H10" t="n">
         <v>200</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29830,8 +29818,6 @@
       <c r="H11" t="n">
         <v>150</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29862,8 +29848,6 @@
       <c r="H12" t="n">
         <v>150</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30014,8 +29998,11 @@
       <c r="H16" t="n">
         <v>150</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -30028,17 +30015,21 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
+        <v>100</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>未参训</t>
+          <t>单练(未参加比赛环节)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -30112,8 +30103,6 @@
       <c r="H19" t="n">
         <v>200</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -30144,8 +30133,6 @@
       <c r="H20" t="n">
         <v>150</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -30198,7 +30185,6 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>2</v>
       </c>
@@ -30208,8 +30194,6 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>脚趾恢复中，未参训</t>
@@ -30250,8 +30234,6 @@
       <c r="H23" t="n">
         <v>250</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -30282,8 +30264,6 @@
       <c r="H24" t="n">
         <v>150</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -30314,8 +30294,11 @@
       <c r="H25" t="n">
         <v>100</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -30353,7 +30336,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MD-3峰值可接受</t>
+          <t>单练(未参加比赛环节)</t>
         </is>
       </c>
     </row>
@@ -30368,18 +30351,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>未参训</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -30393,7 +30369,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -30408,10 +30384,8 @@
         <v>50</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>250</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -30442,8 +30416,6 @@
       <c r="H29" t="n">
         <v>150</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -30514,8 +30486,6 @@
       <c r="H31" t="n">
         <v>200</v>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -30546,8 +30516,6 @@
       <c r="H32" t="n">
         <v>200</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -30578,8 +30546,6 @@
       <c r="H33" t="n">
         <v>200</v>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="34" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="35" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30032,7 +30033,6 @@
           <t>单练(未参加比赛环节)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -30546,6 +30546,922 @@
       <c r="H33" t="n">
         <v>200</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MD-2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>训练50min·下午赶客场青岛</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>150</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>150</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
+        <v>150</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>150</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>150</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>150</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" t="n">
+        <v>150</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>150</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
+        <v>150</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" t="n">
+        <v>150</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>单练(黄牌停赛)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="n">
+        <v>150</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
+        <v>150</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" t="n">
+        <v>150</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" t="n">
+        <v>150</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" t="n">
+        <v>150</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="n">
+        <v>150</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H30" t="n">
+        <v>150</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" t="n">
+        <v>150</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>脚崴缺席</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>持续观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -30649,17 +30649,12 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>50</v>
       </c>
       <c r="H4" t="n">
         <v>150</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30675,17 +30670,12 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>50</v>
       </c>
       <c r="H5" t="n">
         <v>150</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30701,17 +30691,12 @@
       <c r="C6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>50</v>
       </c>
       <c r="H6" t="n">
         <v>150</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30727,17 +30712,12 @@
       <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>50</v>
       </c>
       <c r="H7" t="n">
         <v>150</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30753,17 +30733,12 @@
       <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>50</v>
       </c>
       <c r="H8" t="n">
         <v>150</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30779,17 +30754,12 @@
       <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>50</v>
       </c>
       <c r="H9" t="n">
         <v>150</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30805,9 +30775,6 @@
       <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>50</v>
       </c>
@@ -30839,17 +30806,12 @@
       <c r="C11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>50</v>
       </c>
       <c r="H11" t="n">
         <v>150</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30865,9 +30827,6 @@
       <c r="C12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>50</v>
       </c>
@@ -30879,7 +30838,6 @@
           <t>左膝</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30895,17 +30853,12 @@
       <c r="C13" t="n">
         <v>3</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>50</v>
       </c>
       <c r="H13" t="n">
         <v>150</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30921,17 +30874,12 @@
       <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>50</v>
       </c>
       <c r="H14" t="n">
         <v>150</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30947,9 +30895,6 @@
       <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>50</v>
       </c>
@@ -30981,17 +30926,12 @@
       <c r="C16" t="n">
         <v>2</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>50</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31007,17 +30947,12 @@
       <c r="C17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>50</v>
       </c>
       <c r="H17" t="n">
         <v>150</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31033,17 +30968,12 @@
       <c r="C18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>50</v>
       </c>
       <c r="H18" t="n">
         <v>150</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31059,17 +30989,12 @@
       <c r="C19" t="n">
         <v>3</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>50</v>
       </c>
       <c r="H19" t="n">
         <v>150</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -31085,9 +31010,6 @@
       <c r="C20" t="n">
         <v>2</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>50</v>
       </c>
@@ -31119,9 +31041,6 @@
       <c r="C21" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>50</v>
       </c>
@@ -31153,17 +31072,22 @@
       <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>50</v>
       </c>
       <c r="H22" t="n">
         <v>150</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MD-2减量·保持状态</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -31179,17 +31103,12 @@
       <c r="C23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>50</v>
       </c>
       <c r="H23" t="n">
         <v>150</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -31205,9 +31124,6 @@
       <c r="C24" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>50</v>
       </c>
@@ -31239,9 +31155,6 @@
       <c r="C25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>50</v>
       </c>
@@ -31273,17 +31186,12 @@
       <c r="C26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>50</v>
       </c>
       <c r="H26" t="n">
         <v>150</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -31299,17 +31207,12 @@
       <c r="C27" t="n">
         <v>3</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>50</v>
       </c>
       <c r="H27" t="n">
         <v>150</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -31325,17 +31228,12 @@
       <c r="C28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>50</v>
       </c>
       <c r="H28" t="n">
         <v>150</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -31351,17 +31249,12 @@
       <c r="C29" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>50</v>
       </c>
       <c r="H29" t="n">
         <v>150</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -31377,17 +31270,12 @@
       <c r="C30" t="n">
         <v>3</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>50</v>
       </c>
       <c r="H30" t="n">
         <v>150</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -31403,17 +31291,12 @@
       <c r="C31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>50</v>
       </c>
       <c r="H31" t="n">
         <v>150</v>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -31426,12 +31309,6 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>脚崴缺席</t>
@@ -31454,14 +31331,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -30649,6 +30649,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" t="n">
         <v>50</v>
       </c>
@@ -30670,6 +30679,15 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" t="n">
         <v>50</v>
       </c>
@@ -30691,6 +30709,15 @@
       <c r="C6" t="n">
         <v>3</v>
       </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" t="n">
         <v>50</v>
       </c>
@@ -30712,6 +30739,15 @@
       <c r="C7" t="n">
         <v>3</v>
       </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" t="n">
         <v>50</v>
       </c>
@@ -30733,6 +30769,15 @@
       <c r="C8" t="n">
         <v>3</v>
       </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
       <c r="G8" t="n">
         <v>50</v>
       </c>
@@ -30754,6 +30799,15 @@
       <c r="C9" t="n">
         <v>3</v>
       </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
       <c r="G9" t="n">
         <v>50</v>
       </c>
@@ -30775,6 +30829,15 @@
       <c r="C10" t="n">
         <v>3</v>
       </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" t="n">
         <v>50</v>
       </c>
@@ -30806,6 +30869,15 @@
       <c r="C11" t="n">
         <v>3</v>
       </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
       <c r="G11" t="n">
         <v>50</v>
       </c>
@@ -30827,6 +30899,15 @@
       <c r="C12" t="n">
         <v>3</v>
       </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
       <c r="G12" t="n">
         <v>50</v>
       </c>
@@ -30853,6 +30934,15 @@
       <c r="C13" t="n">
         <v>3</v>
       </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
       <c r="G13" t="n">
         <v>50</v>
       </c>
@@ -30874,6 +30964,15 @@
       <c r="C14" t="n">
         <v>3</v>
       </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
       <c r="G14" t="n">
         <v>50</v>
       </c>
@@ -30895,6 +30994,15 @@
       <c r="C15" t="n">
         <v>2</v>
       </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
       <c r="G15" t="n">
         <v>50</v>
       </c>
@@ -30926,6 +31034,9 @@
       <c r="C16" t="n">
         <v>2</v>
       </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" t="n">
         <v>50</v>
       </c>
@@ -30947,6 +31058,15 @@
       <c r="C17" t="n">
         <v>3</v>
       </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" t="n">
         <v>50</v>
       </c>
@@ -30968,6 +31088,15 @@
       <c r="C18" t="n">
         <v>3</v>
       </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
       <c r="G18" t="n">
         <v>50</v>
       </c>
@@ -30989,6 +31118,15 @@
       <c r="C19" t="n">
         <v>3</v>
       </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" t="n">
         <v>50</v>
       </c>
@@ -31010,6 +31148,15 @@
       <c r="C20" t="n">
         <v>2</v>
       </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
       <c r="G20" t="n">
         <v>50</v>
       </c>
@@ -31041,6 +31188,15 @@
       <c r="C21" t="n">
         <v>2</v>
       </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
@@ -31072,6 +31228,15 @@
       <c r="C22" t="n">
         <v>3</v>
       </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
       <c r="G22" t="n">
         <v>50</v>
       </c>
@@ -31103,6 +31268,15 @@
       <c r="C23" t="n">
         <v>3</v>
       </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
       <c r="G23" t="n">
         <v>50</v>
       </c>
@@ -31124,6 +31298,15 @@
       <c r="C24" t="n">
         <v>2</v>
       </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" t="n">
         <v>50</v>
       </c>
@@ -31155,6 +31338,15 @@
       <c r="C25" t="n">
         <v>2</v>
       </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
       <c r="G25" t="n">
         <v>50</v>
       </c>
@@ -31186,6 +31378,15 @@
       <c r="C26" t="n">
         <v>3</v>
       </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
       <c r="G26" t="n">
         <v>50</v>
       </c>
@@ -31207,6 +31408,15 @@
       <c r="C27" t="n">
         <v>3</v>
       </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
       <c r="G27" t="n">
         <v>50</v>
       </c>
@@ -31228,6 +31438,15 @@
       <c r="C28" t="n">
         <v>3</v>
       </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
       <c r="G28" t="n">
         <v>50</v>
       </c>
@@ -31249,6 +31468,15 @@
       <c r="C29" t="n">
         <v>3</v>
       </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
       <c r="G29" t="n">
         <v>50</v>
       </c>
@@ -31270,6 +31498,15 @@
       <c r="C30" t="n">
         <v>3</v>
       </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
       <c r="G30" t="n">
         <v>50</v>
       </c>
@@ -31291,6 +31528,15 @@
       <c r="C31" t="n">
         <v>3</v>
       </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
       <c r="G31" t="n">
         <v>50</v>
       </c>
@@ -31308,6 +31554,15 @@
         <is>
           <t>GK</t>
         </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="35" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="36" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.14" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -31592,6 +31593,1011 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MD-1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>踩场减量+冲刺激活·50min</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>250</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="n">
+        <v>200</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" t="n">
+        <v>150</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>略不舒服</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="n">
+        <v>150</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="n">
+        <v>250</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" t="n">
+        <v>250</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>200</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="n">
+        <v>250</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
+        <v>200</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" t="n">
+        <v>200</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="n">
+        <v>100</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" t="n">
+        <v>200</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
+        <v>250</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" t="n">
+        <v>250</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>黄牌停赛·未跟队</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="36" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="11120" tabRatio="600" firstSheet="29" activeTab="37" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.06" sheetId="1" state="visible" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.14" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.15" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -7930,7 +7931,7 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>2</v>
@@ -7942,10 +7943,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -7970,7 +7971,7 @@
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>2</v>
@@ -7982,10 +7983,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>300</v>
+        <v>770</v>
       </c>
       <c r="I6" s="15" t="inlineStr"/>
       <c r="J6" s="15" t="inlineStr">
@@ -8006,7 +8007,7 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>2</v>
@@ -8018,10 +8019,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>300</v>
+        <v>770</v>
       </c>
       <c r="I7" s="15" t="inlineStr"/>
       <c r="J7" s="15" t="inlineStr">
@@ -8042,7 +8043,7 @@
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>3</v>
@@ -8054,10 +8055,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
@@ -8094,10 +8095,10 @@
         <v>3</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
@@ -8122,7 +8123,7 @@
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>3</v>
@@ -8134,10 +8135,10 @@
         <v>2</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>300</v>
+        <v>710</v>
       </c>
       <c r="I10" s="15" t="inlineStr"/>
       <c r="J10" s="15" t="inlineStr">
@@ -8158,7 +8159,7 @@
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>2</v>
@@ -8170,10 +8171,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>300</v>
+        <v>770</v>
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
@@ -8198,7 +8199,7 @@
         </is>
       </c>
       <c r="C12" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>3</v>
@@ -8210,10 +8211,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I12" s="15" t="inlineStr"/>
       <c r="J12" s="15" t="inlineStr">
@@ -8234,7 +8235,7 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>3</v>
@@ -8246,10 +8247,10 @@
         <v>3</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>300</v>
+        <v>770</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
@@ -8274,7 +8275,7 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>3</v>
@@ -8286,10 +8287,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>300</v>
+        <v>710</v>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
@@ -8314,7 +8315,7 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>3</v>
@@ -8326,10 +8327,10 @@
         <v>3</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>300</v>
+        <v>770</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
@@ -8354,7 +8355,7 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>4</v>
@@ -8366,10 +8367,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -8394,7 +8395,7 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>3</v>
@@ -8406,10 +8407,10 @@
         <v>3</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>300</v>
+        <v>710</v>
       </c>
       <c r="I17" s="15" t="inlineStr"/>
       <c r="J17" s="15" t="inlineStr">
@@ -8430,7 +8431,7 @@
         </is>
       </c>
       <c r="C18" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>3</v>
@@ -8442,10 +8443,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I18" s="15" t="inlineStr"/>
       <c r="J18" s="15" t="inlineStr">
@@ -8466,7 +8467,7 @@
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>5</v>
@@ -8478,10 +8479,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -8506,7 +8507,7 @@
         </is>
       </c>
       <c r="C20" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>3</v>
@@ -8522,10 +8523,10 @@
         </is>
       </c>
       <c r="G20" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
@@ -8550,7 +8551,7 @@
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>3</v>
@@ -8566,10 +8567,10 @@
         </is>
       </c>
       <c r="G21" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
@@ -8594,7 +8595,7 @@
         </is>
       </c>
       <c r="C22" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>4</v>
@@ -8606,10 +8607,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
@@ -8634,7 +8635,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>3</v>
@@ -8646,10 +8647,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
@@ -8674,7 +8675,7 @@
         </is>
       </c>
       <c r="C24" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>3</v>
@@ -8686,10 +8687,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="I24" s="15" t="inlineStr"/>
       <c r="J24" s="15" t="inlineStr">
@@ -8710,7 +8711,7 @@
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>4</v>
@@ -8722,10 +8723,10 @@
         <v>2</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I25" s="15" t="inlineStr"/>
       <c r="J25" s="15" t="inlineStr">
@@ -8746,7 +8747,7 @@
         </is>
       </c>
       <c r="C26" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>3</v>
@@ -8758,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I26" s="15" t="inlineStr"/>
       <c r="J26" s="15" t="inlineStr">
@@ -8782,7 +8783,7 @@
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>3</v>
@@ -8794,10 +8795,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I27" s="15" t="inlineStr"/>
       <c r="J27" s="15" t="inlineStr">
@@ -8834,10 +8835,10 @@
         </is>
       </c>
       <c r="G28" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
@@ -8862,7 +8863,7 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>2</v>
@@ -8874,10 +8875,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>180</v>
+        <v>510</v>
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
@@ -8952,7 +8953,7 @@
         </is>
       </c>
       <c r="C31" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>2</v>
@@ -8964,10 +8965,10 @@
         <v>3</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="I31" s="15" t="inlineStr"/>
       <c r="J31" s="15" t="inlineStr">
@@ -8988,7 +8989,7 @@
         </is>
       </c>
       <c r="C32" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>2</v>
@@ -9000,10 +9001,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>300</v>
+        <v>710</v>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
@@ -9028,7 +9029,7 @@
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>4</v>
@@ -9040,10 +9041,10 @@
         <v>3</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
@@ -9068,7 +9069,7 @@
         </is>
       </c>
       <c r="C34" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>3</v>
@@ -9080,10 +9081,10 @@
         <v>2</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="I34" s="15" t="inlineStr"/>
       <c r="J34" s="15" t="inlineStr">
@@ -9104,7 +9105,7 @@
         </is>
       </c>
       <c r="C35" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>3</v>
@@ -9116,10 +9117,10 @@
         <v>2</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="I35" s="15" t="inlineStr"/>
       <c r="J35" s="15" t="inlineStr"/>
@@ -31710,7 +31711,6 @@
           <t>脚踝痛</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31746,7 +31746,6 @@
           <t>腰疼</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31777,8 +31776,6 @@
       <c r="H6" t="n">
         <v>150</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31814,7 +31811,6 @@
           <t>略不舒服</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31845,8 +31841,6 @@
       <c r="H8" t="n">
         <v>150</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31877,8 +31871,6 @@
       <c r="H9" t="n">
         <v>300</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31909,8 +31901,6 @@
       <c r="H10" t="n">
         <v>250</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31941,8 +31931,6 @@
       <c r="H11" t="n">
         <v>250</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31978,7 +31966,6 @@
           <t>左膝</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32009,8 +31996,6 @@
       <c r="H13" t="n">
         <v>250</v>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32041,8 +32026,6 @@
       <c r="H14" t="n">
         <v>200</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32073,8 +32056,6 @@
       <c r="H15" t="n">
         <v>200</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32105,8 +32086,6 @@
       <c r="H16" t="n">
         <v>250</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32134,8 +32113,6 @@
       <c r="H17" t="n">
         <v>200</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32166,8 +32143,6 @@
       <c r="H18" t="n">
         <v>200</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32198,8 +32173,6 @@
       <c r="H19" t="n">
         <v>150</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32230,8 +32203,6 @@
       <c r="H20" t="n">
         <v>100</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -32262,8 +32233,6 @@
       <c r="H21" t="n">
         <v>50</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -32294,8 +32263,6 @@
       <c r="H22" t="n">
         <v>200</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -32326,8 +32293,6 @@
       <c r="H23" t="n">
         <v>250</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -32358,8 +32323,6 @@
       <c r="H24" t="n">
         <v>250</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -32390,8 +32353,6 @@
       <c r="H25" t="n">
         <v>200</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -32422,8 +32383,6 @@
       <c r="H26" t="n">
         <v>250</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -32436,18 +32395,11 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -32460,18 +32412,11 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -32484,18 +32429,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>黄牌停赛·未跟队</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -32508,18 +32446,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>未跟队</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -32532,18 +32463,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>未跟队</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -32556,18 +32480,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>未跟队</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -32580,18 +32497,1083 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>中乙第21轮 客vs青岛红狮 0-1负 · 90min · 5-3-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>90</v>
+      </c>
+      <c r="H4" t="n">
+        <v>720</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>首发全场·脚踝</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>D+1冰敷踝泵</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>45</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H8" t="n">
+        <v>900</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>首发全场·RPE=10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>D+1泳池恢复优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" t="n">
+        <v>720</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63</v>
+      </c>
+      <c r="H10" t="n">
+        <v>441</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>首发63'↓</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>45</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" t="n">
+        <v>45</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>90</v>
+      </c>
+      <c r="H14" t="n">
+        <v>720</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H15" t="n">
+        <v>720</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>79</v>
+      </c>
+      <c r="H18" t="n">
+        <v>711</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>首发79'↓</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>189</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>63'↑·MCL首秀</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>D+1观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>448</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>首发56'↓</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>黄牌停赛·未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>90</v>
+      </c>
+      <c r="H29" t="n">
+        <v>810</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>90</v>
+      </c>
+      <c r="H30" t="n">
+        <v>810</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>首发全场·队长</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>90</v>
+      </c>
+      <c r="H31" t="n">
+        <v>900</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>首发全场·RPE=10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>D+1泳池恢复优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34</v>
+      </c>
+      <c r="H32" t="n">
+        <v>238</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>56'↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>88</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>79'↑</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日强度监控.xlsx
+++ b/public/share/data/每日强度监控.xlsx
@@ -2054,18 +2054,12 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C20" s="34" t="n">
-        <v>5</v>
-      </c>
+      <c r="C20" s="34" t="n"/>
       <c r="D20" s="34" t="inlineStr"/>
       <c r="E20" s="34" t="inlineStr"/>
       <c r="F20" s="34" t="inlineStr"/>
-      <c r="G20" s="34" t="n">
-        <v>45</v>
-      </c>
-      <c r="H20" s="34" t="n">
-        <v>225</v>
-      </c>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
       <c r="I20" s="34" t="inlineStr"/>
       <c r="J20" s="34" t="inlineStr">
         <is>
@@ -4387,12 +4381,18 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
+      <c r="C29" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="30" ht="17.6" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -7279,6 +7279,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -7715,6 +7716,15 @@
         <is>
           <t>MID</t>
         </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" t="n">
+        <v>200</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -10170,9 +10180,7 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>3</v>
-      </c>
+      <c r="C29" s="16" t="n"/>
       <c r="D29" s="16" t="n">
         <v>2</v>
       </c>
@@ -10182,12 +10190,8 @@
       <c r="F29" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>180</v>
-      </c>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
       <c r="I29" s="15" t="inlineStr">
         <is>
           <t>新人·全部缺填</t>
@@ -10366,9 +10370,7 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C34" s="16" t="n">
-        <v>4</v>
-      </c>
+      <c r="C34" s="16" t="n"/>
       <c r="D34" s="16" t="n">
         <v>3</v>
       </c>
@@ -10378,12 +10380,8 @@
       <c r="F34" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>240</v>
-      </c>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
       <c r="I34" s="15" t="inlineStr">
         <is>
           <t>租借离队→海门珂缔缘</t>
@@ -21602,7 +21600,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RPE</t>
+          <t>RPE(0-10)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -21622,7 +21620,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>时长</t>
+          <t>时长(min)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -21654,7 +21652,9 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n"/>
+      <c r="C2" s="1" t="n">
+        <v>5</v>
+      </c>
       <c r="D2" s="1" t="n">
         <v>3</v>
       </c>
@@ -21664,8 +21664,12 @@
       <c r="F2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
+      <c r="G2" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>190</v>
+      </c>
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
@@ -21686,7 +21690,9 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n"/>
+      <c r="C3" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D3" s="1" t="n">
         <v>3</v>
       </c>
@@ -21696,8 +21702,12 @@
       <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
+      <c r="G3" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I3" s="1" t="n"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
@@ -21718,7 +21728,9 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n"/>
+      <c r="C4" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D4" s="1" t="n">
         <v>3</v>
       </c>
@@ -21728,8 +21740,12 @@
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
+      <c r="G4" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I4" s="1" t="n"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
@@ -21776,7 +21792,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n"/>
+      <c r="C6" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D6" s="1" t="n">
         <v>2</v>
       </c>
@@ -21786,8 +21804,12 @@
       <c r="F6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
+      <c r="G6" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
           <t>紧</t>
@@ -21812,7 +21834,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n"/>
+      <c r="C7" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D7" s="1" t="n">
         <v>2</v>
       </c>
@@ -21822,8 +21846,12 @@
       <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="1" t="n"/>
-      <c r="H7" s="1" t="n"/>
+      <c r="G7" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I7" s="1" t="n"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
@@ -21844,7 +21872,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n"/>
+      <c r="C8" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D8" s="1" t="n">
         <v>2</v>
       </c>
@@ -21854,8 +21884,12 @@
       <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="1" t="n"/>
-      <c r="H8" s="1" t="n"/>
+      <c r="G8" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I8" s="1" t="n"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
@@ -21876,7 +21910,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n"/>
+      <c r="C9" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D9" s="1" t="n">
         <v>3</v>
       </c>
@@ -21886,8 +21922,12 @@
       <c r="F9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
+      <c r="G9" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I9" s="1" t="n"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -21908,7 +21948,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n"/>
+      <c r="C10" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
       </c>
@@ -21918,8 +21960,12 @@
       <c r="F10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
+      <c r="G10" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
           <t>右膝</t>
@@ -21944,7 +21990,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n"/>
+      <c r="C11" s="1" t="n">
+        <v>5</v>
+      </c>
       <c r="D11" s="1" t="n">
         <v>3</v>
       </c>
@@ -21954,8 +22002,12 @@
       <c r="F11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
+      <c r="G11" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>190</v>
+      </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>左膝</t>
@@ -21980,7 +22032,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n"/>
+      <c r="C12" s="1" t="n">
+        <v>5</v>
+      </c>
       <c r="D12" s="1" t="n">
         <v>2</v>
       </c>
@@ -21990,8 +22044,12 @@
       <c r="F12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
+      <c r="G12" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>190</v>
+      </c>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -22012,7 +22070,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n"/>
+      <c r="C13" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D13" s="1" t="n">
         <v>3</v>
       </c>
@@ -22022,8 +22082,12 @@
       <c r="F13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
+      <c r="G13" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I13" s="1" t="n"/>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -22044,7 +22108,9 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n"/>
+      <c r="C14" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D14" s="1" t="n">
         <v>3</v>
       </c>
@@ -22054,8 +22120,12 @@
       <c r="F14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
+      <c r="G14" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I14" s="1" t="n"/>
       <c r="J14" s="1" t="inlineStr">
         <is>
@@ -22102,7 +22172,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n"/>
+      <c r="C16" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D16" s="1" t="n">
         <v>2</v>
       </c>
@@ -22112,8 +22184,12 @@
       <c r="F16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
+      <c r="G16" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -22134,7 +22210,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n"/>
+      <c r="C17" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D17" s="1" t="n">
         <v>2</v>
       </c>
@@ -22144,8 +22222,12 @@
       <c r="F17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
+      <c r="G17" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -22166,7 +22248,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n"/>
+      <c r="C18" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D18" s="1" t="n">
         <v>2</v>
       </c>
@@ -22176,8 +22260,12 @@
       <c r="F18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="1" t="n"/>
-      <c r="H18" s="1" t="n"/>
+      <c r="G18" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I18" s="1" t="n"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -22198,7 +22286,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n"/>
+      <c r="C19" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D19" s="1" t="n">
         <v>2</v>
       </c>
@@ -22208,8 +22298,12 @@
       <c r="F19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="1" t="n"/>
-      <c r="H19" s="1" t="n"/>
+      <c r="G19" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I19" s="1" t="n"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
@@ -22230,7 +22324,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n"/>
+      <c r="C20" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D20" s="1" t="n">
         <v>2</v>
       </c>
@@ -22240,8 +22336,12 @@
       <c r="F20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="1" t="n"/>
-      <c r="H20" s="1" t="n"/>
+      <c r="G20" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I20" s="1" t="n"/>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -22262,7 +22362,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n"/>
+      <c r="C21" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D21" s="1" t="n">
         <v>3</v>
       </c>
@@ -22272,8 +22374,12 @@
       <c r="F21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
+      <c r="G21" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I21" s="1" t="n"/>
       <c r="J21" s="1" t="inlineStr">
         <is>
@@ -22294,7 +22400,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n"/>
+      <c r="C22" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D22" s="1" t="n">
         <v>2</v>
       </c>
@@ -22304,8 +22412,12 @@
       <c r="F22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
+      <c r="G22" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="inlineStr">
         <is>
@@ -22326,7 +22438,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n"/>
+      <c r="C23" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
@@ -22336,8 +22450,12 @@
       <c r="F23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
+      <c r="G23" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I23" s="1" t="n"/>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -22436,7 +22554,9 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n"/>
+      <c r="C27" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="D27" s="1" t="n">
         <v>1</v>
       </c>
@@ -22446,8 +22566,12 @@
       <c r="F27" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
+      <c r="G27" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>114</v>
+      </c>
       <c r="I27" s="1" t="n"/>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -22468,7 +22592,9 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n"/>
+      <c r="C28" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D28" s="1" t="n">
         <v>2</v>
       </c>
@@ -22478,8 +22604,12 @@
       <c r="F28" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
+      <c r="G28" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
           <t>微酸</t>
@@ -22504,7 +22634,9 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n"/>
+      <c r="C29" s="1" t="n">
+        <v>5</v>
+      </c>
       <c r="D29" s="1" t="n">
         <v>3</v>
       </c>
@@ -22514,8 +22646,12 @@
       <c r="F29" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="n"/>
+      <c r="G29" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>190</v>
+      </c>
       <c r="I29" s="1" t="n"/>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -22536,7 +22672,9 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n"/>
+      <c r="C30" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D30" s="1" t="n">
         <v>3</v>
       </c>
@@ -22546,8 +22684,12 @@
       <c r="F30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
+      <c r="G30" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I30" s="1" t="n"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -22568,7 +22710,9 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n"/>
+      <c r="C31" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="D31" s="1" t="n">
         <v>3</v>
       </c>
@@ -22578,8 +22722,12 @@
       <c r="F31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
+      <c r="G31" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>152</v>
+      </c>
       <c r="I31" s="1" t="n"/>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -23254,9 +23402,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="C17" s="1" t="n"/>
       <c r="D17" s="1" t="n">
         <v>3</v>
       </c>
@@ -23266,12 +23412,8 @@
       <c r="F17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>20</v>
-      </c>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
@@ -23324,9 +23466,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>4</v>
-      </c>
+      <c r="C19" s="1" t="n"/>
       <c r="D19" s="1" t="n">
         <v>3</v>
       </c>
@@ -23336,12 +23476,8 @@
       <c r="F19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>40</v>
-      </c>
+      <c r="G19" s="1" t="n"/>
+      <c r="H19" s="1" t="n"/>
       <c r="I19" s="1" t="n"/>
       <c r="J19" s="1" t="n"/>
       <c r="K19" s="1" t="n"/>
@@ -23357,9 +23493,7 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>3</v>
-      </c>
+      <c r="C20" s="1" t="n"/>
       <c r="D20" s="1" t="n">
         <v>3</v>
       </c>
@@ -23369,12 +23503,8 @@
       <c r="F20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>30</v>
-      </c>
+      <c r="G20" s="1" t="n"/>
+      <c r="H20" s="1" t="n"/>
       <c r="I20" s="1" t="n"/>
       <c r="J20" s="1" t="n"/>
       <c r="K20" s="1" t="n"/>
@@ -23390,9 +23520,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="C21" s="1" t="n"/>
       <c r="D21" s="1" t="n">
         <v>3</v>
       </c>
@@ -23402,12 +23530,8 @@
       <c r="F21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>20</v>
-      </c>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
       <c r="I21" s="1" t="n"/>
       <c r="J21" s="1" t="n"/>
       <c r="K21" s="1" t="n"/>
@@ -23423,9 +23547,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>4</v>
-      </c>
+      <c r="C22" s="1" t="n"/>
       <c r="D22" s="1" t="n">
         <v>2</v>
       </c>
@@ -23435,12 +23557,8 @@
       <c r="F22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>40</v>
-      </c>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
       <c r="I22" s="1" t="n"/>
       <c r="J22" s="1" t="n"/>
       <c r="K22" s="1" t="n"/>
@@ -23456,9 +23574,7 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>6</v>
-      </c>
+      <c r="C23" s="1" t="n"/>
       <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
@@ -23468,12 +23584,8 @@
       <c r="F23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>60</v>
-      </c>
+      <c r="G23" s="1" t="n"/>
+      <c r="H23" s="1" t="n"/>
       <c r="I23" s="1" t="n"/>
       <c r="J23" s="1" t="n"/>
       <c r="K23" s="1" t="n"/>
@@ -23489,9 +23601,7 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>3</v>
-      </c>
+      <c r="C24" s="1" t="n"/>
       <c r="D24" s="1" t="n">
         <v>2</v>
       </c>
@@ -23501,12 +23611,8 @@
       <c r="F24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>30</v>
-      </c>
+      <c r="G24" s="1" t="n"/>
+      <c r="H24" s="1" t="n"/>
       <c r="I24" s="1" t="n"/>
       <c r="J24" s="1" t="n"/>
       <c r="K24" s="1" t="n"/>
@@ -23522,9 +23628,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>4</v>
-      </c>
+      <c r="C25" s="1" t="n"/>
       <c r="D25" s="1" t="n">
         <v>3</v>
       </c>
@@ -23534,12 +23638,8 @@
       <c r="F25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>40</v>
-      </c>
+      <c r="G25" s="1" t="n"/>
+      <c r="H25" s="1" t="n"/>
       <c r="I25" s="1" t="n"/>
       <c r="J25" s="1" t="n"/>
       <c r="K25" s="1" t="n"/>
@@ -31557,6 +31657,9 @@
           <t>GK</t>
         </is>
       </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
@@ -31566,9 +31669,15 @@
       <c r="F32" t="n">
         <v>2</v>
       </c>
+      <c r="G32" t="n">
+        <v>50</v>
+      </c>
+      <c r="H32" t="n">
+        <v>150</v>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>脚崴缺席</t>
+          <t>脚踝疼</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -34926,9 +35035,7 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
-        <v>5</v>
-      </c>
+      <c r="C14" s="34" t="n"/>
       <c r="D14" s="34" t="n">
         <v>2</v>
       </c>
@@ -34938,12 +35045,8 @@
       <c r="F14" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="34" t="n">
-        <v>50</v>
-      </c>
-      <c r="H14" s="34" t="n">
-        <v>250</v>
-      </c>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="34" t="n"/>
       <c r="I14" s="34" t="inlineStr"/>
       <c r="J14" s="34" t="inlineStr">
         <is>
@@ -38980,12 +39083,18 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr"/>
+      <c r="C19" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="D19" s="26" t="inlineStr"/>
       <c r="E19" s="26" t="inlineStr"/>
       <c r="F19" s="26" t="inlineStr"/>
-      <c r="G19" s="26" t="inlineStr"/>
-      <c r="H19" s="26" t="inlineStr"/>
+      <c r="G19" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>200</v>
+      </c>
       <c r="I19" s="28" t="inlineStr"/>
       <c r="J19" s="29" t="inlineStr">
         <is>
